--- a/12621579.xlsx
+++ b/12621579.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5a674bc83430fa5a/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5a674bc83430fa5a/Desktop/daily routine/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="19" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D89C6AEB-CB13-43E6-B419-3B6A6A6C7C2A}"/>
+  <xr:revisionPtr revIDLastSave="31" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{129B753C-8BA0-4568-9AFA-87A4734005D4}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="59">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -200,6 +200,18 @@
   </si>
   <si>
     <t xml:space="preserve">C++ Coding </t>
+  </si>
+  <si>
+    <t>Good</t>
+  </si>
+  <si>
+    <t>Satisfied</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>SQL</t>
   </si>
 </sst>
 </file>
@@ -1026,26 +1038,50 @@
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A7" s="13"/>
-      <c r="B7" s="14"/>
-      <c r="C7" s="14"/>
-      <c r="D7" s="14"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="14"/>
-      <c r="G7" s="14"/>
-      <c r="H7" s="14"/>
-      <c r="I7" s="15" t="str">
+      <c r="A7" s="13">
+        <v>46254</v>
+      </c>
+      <c r="B7" s="14">
+        <v>300</v>
+      </c>
+      <c r="C7" s="14">
+        <v>0</v>
+      </c>
+      <c r="D7" s="14">
+        <v>180</v>
+      </c>
+      <c r="E7" s="14">
+        <v>60</v>
+      </c>
+      <c r="F7" s="14">
+        <v>150</v>
+      </c>
+      <c r="G7" s="14">
+        <v>3</v>
+      </c>
+      <c r="H7" s="14">
+        <v>120</v>
+      </c>
+      <c r="I7" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J7" s="15" t="str">
+        <v>810</v>
+      </c>
+      <c r="J7" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K7" s="16"/>
-      <c r="L7" s="16"/>
-      <c r="M7" s="16"/>
-      <c r="N7" s="17"/>
+        <v>630</v>
+      </c>
+      <c r="K7" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="L7" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M7" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N7" s="17" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" s="13"/>

--- a/12621579.xlsx
+++ b/12621579.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5a674bc83430fa5a/Desktop/daily routine/CAP776/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aayus\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="31" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{129B753C-8BA0-4568-9AFA-87A4734005D4}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{572A291E-042A-4AD7-A5AA-835FD725713A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="57">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -184,6 +184,18 @@
     <t>Notes</t>
   </si>
   <si>
+    <t>Good</t>
+  </si>
+  <si>
+    <t>Satisfied</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>Example row — replace with your own data. Felt a bit tired after evening class.</t>
+  </si>
+  <si>
     <t>5. GOOD PRACTICE</t>
   </si>
   <si>
@@ -193,25 +205,7 @@
     <t>MCA D1P2632</t>
   </si>
   <si>
-    <t>Neutral</t>
-  </si>
-  <si>
-    <t>Low</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C++ Coding </t>
-  </si>
-  <si>
-    <t>Good</t>
-  </si>
-  <si>
-    <t>Satisfied</t>
-  </si>
-  <si>
-    <t>Medium</t>
-  </si>
-  <si>
-    <t>SQL</t>
+    <t>Felt good today</t>
   </si>
 </sst>
 </file>
@@ -350,7 +344,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -394,7 +388,6 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="17" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -830,7 +823,7 @@
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A33" s="5" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.3">
@@ -866,8 +859,10 @@
   <dimension ref="A1:N401"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="6" width="11" customWidth="1"/>
+    <col min="1" max="1" width="25.109375" customWidth="1"/>
+    <col min="2" max="4" width="11" customWidth="1"/>
+    <col min="5" max="5" width="18.88671875" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
     <col min="7" max="7" width="13" customWidth="1"/>
     <col min="8" max="9" width="14" customWidth="1"/>
     <col min="10" max="10" width="15" customWidth="1"/>
@@ -900,7 +895,7 @@
         <v>30</v>
       </c>
       <c r="B2" s="20" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C2" s="20"/>
       <c r="D2" s="20"/>
@@ -917,16 +912,14 @@
         <v>32</v>
       </c>
       <c r="B3" s="20" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C3" s="20"/>
       <c r="D3" s="20"/>
       <c r="E3" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="F3" s="21">
-        <v>46235</v>
-      </c>
+      <c r="F3" s="20"/>
       <c r="G3" s="20"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
@@ -991,96 +984,96 @@
         <v>48</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A6" s="8">
-        <v>46253</v>
+        <v>46223</v>
       </c>
       <c r="B6" s="9">
-        <v>300</v>
+        <v>420</v>
       </c>
       <c r="C6" s="9">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="D6" s="9">
-        <v>240</v>
+        <v>120</v>
       </c>
       <c r="E6" s="9">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="F6" s="9">
-        <v>350</v>
+        <v>180</v>
       </c>
       <c r="G6" s="9">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H6" s="9">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="I6" s="10">
         <f t="shared" ref="I6:I69" si="0">IF(SUM(B6:F6,H6)=0,"",SUM(B6:F6,H6))</f>
-        <v>1100</v>
+        <v>885</v>
       </c>
       <c r="J6" s="10">
         <f t="shared" ref="J6:J69" si="1">IF(I6="","",1440-I6)</f>
-        <v>340</v>
+        <v>555</v>
       </c>
       <c r="K6" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L6" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M6" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N6" s="12" t="s">
         <v>52</v>
-      </c>
-      <c r="L6" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="M6" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="N6" s="12" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" s="13">
-        <v>46254</v>
+        <v>46262</v>
       </c>
       <c r="B7" s="14">
-        <v>300</v>
+        <v>420</v>
       </c>
       <c r="C7" s="14">
         <v>0</v>
       </c>
       <c r="D7" s="14">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="E7" s="14">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="F7" s="14">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="G7" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H7" s="14">
         <v>120</v>
       </c>
       <c r="I7" s="15">
         <f t="shared" si="0"/>
-        <v>810</v>
+        <v>860</v>
       </c>
       <c r="J7" s="15">
         <f t="shared" si="1"/>
-        <v>630</v>
+        <v>580</v>
       </c>
       <c r="K7" s="16" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="L7" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M7" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N7" s="17" t="s">
         <v>56</v>
-      </c>
-      <c r="M7" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="N7" s="17" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
